--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_recheckthresh.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_recheckthresh.xlsx
@@ -53,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,13 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +168,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -789,16 +789,16 @@
       <c r="C4" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="12" t="n">
         <v>11.5</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -816,11 +816,11 @@
       <c r="L4" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>29.5</v>
+      <c r="N4" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -828,7 +828,7 @@
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -838,13 +838,13 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>18.7</v>
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -864,76 +864,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F5" s="11" t="n">
+        <v>388.3</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F5" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.8</v>
+      <c r="H5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L5" s="15" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q5" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W5" s="11" t="n">
-        <v>17.6</v>
+        <v>13</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
+        <v>13.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -949,48 +949,48 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G6" s="11" t="n">
+        <v>508.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.1</v>
+        <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -1000,25 +1000,25 @@
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.5</v>
+        <v>18.5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>10.4</v>
+        <v>512.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>16.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27</v>
+        <v>17.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1034,76 +1034,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>10.7</v>
+        <v>22.9</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>7.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>98</v>
+        <v>29.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15.8</v>
+        <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>52.4</v>
+        <v>22.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R7" s="15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.1</v>
+        <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V7" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>16.6</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.5</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1119,76 +1119,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>7.7</v>
+        <v>22.2</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>50.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>63.1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.9</v>
+        <v>706.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.8</v>
+        <v>260.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>14.1</v>
+        <v>51.1</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>60.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>40.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.6</v>
+        <v>59</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>11.4</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1204,75 +1204,77 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>222.4</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>1118.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>30.9</v>
+        <v>445</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>10.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.1</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>706.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>260.4</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="10" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>0.2</v>
+      <c r="L9" s="14" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59</v>
+        <v>21.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>114</v>
-      </c>
-      <c r="R9" s="10" t="n">
-        <v>88.09999999999999</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q9" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <v>17.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.2</v>
+        <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>212.6</v>
+        <v>21.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V9" s="10" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="W9" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V9" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="W9" s="14" t="n">
         <v>16</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>117.8</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1287,74 +1289,76 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J10" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M10" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="N10" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>15.8</v>
-      </c>
       <c r="O10" s="3" t="n">
-        <v>99.8</v>
+        <v>15.3</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="Q10" s="14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q10" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="14" t="n">
         <v>17.6</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="14" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="14" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>83</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1372,17 +1376,17 @@
       <c r="C11" s="3" t="n">
         <v>191.8</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>28.8</v>
+      <c r="G11" s="12" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
@@ -1394,53 +1398,43 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.9</v>
+        <v>17.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q11" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="R11" s="15" t="n">
-        <v>1.1</v>
+      <c r="Q11" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>17.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>140649.1</v>
+        <v>212.4</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="W11" s="15" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>717.5</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>80494</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="11" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1457,19 +1451,19 @@
       <c r="C12" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>9.1</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1481,40 +1475,40 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>83.90000000000001</v>
+      <c r="M12" s="12" t="n">
+        <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R12" s="3" t="n">
+      <c r="Q12" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R12" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>24.8</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="15" t="n">
+      <c r="V12" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="W12" s="13" t="inlineStr"/>
+      <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1538,20 +1532,20 @@
       <c r="C13" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>18.7</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1565,35 +1559,35 @@
       <c r="L13" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="12" t="n">
         <v>15.8</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.9</v>
+        <v>74.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>14.8</v>
@@ -1621,76 +1615,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>56.8</v>
+        <v>26.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W14" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1708,49 +1702,49 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="E15" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>25</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1760,7 +1754,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1793,50 +1787,50 @@
       <c r="C16" s="3" t="n">
         <v>147.5</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="D16" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E16" s="14" t="n">
         <v>674.7</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>9.199999999999999</v>
+      <c r="F16" s="14" t="n">
+        <v>92.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>164.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L16" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="L16" s="14" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="14" t="n">
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1140.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>83</v>
+      <c r="R16" s="12" t="n">
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1845,19 +1839,19 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V16" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V16" s="14" t="n">
         <v>84.3</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="14" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1208.8</v>
+        <v>158.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1876,16 +1870,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>295</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>12.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1897,30 +1891,30 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="L17" s="10" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L17" s="14" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <v>19.1</v>
+      <c r="M17" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="12" t="n">
         <v>19.3</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1930,19 +1924,19 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="V17" s="10" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="V17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>15.3</v>
@@ -1961,25 +1955,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.3</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="E18" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>48.4</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1987,10 +1981,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -2000,10 +1994,10 @@
         <v>91</v>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2013,16 +2007,16 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V18" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="X18" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>84</v>
@@ -2044,18 +2038,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>440.6</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2070,25 +2064,25 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="15" t="n">
-        <v>1.4</v>
+      <c r="M19" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R19" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R19" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2100,11 +2094,11 @@
       <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W19" s="15" t="n">
-        <v>87</v>
+      <c r="V19" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W19" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>18.3</v>
@@ -2113,7 +2107,7 @@
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>17.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2131,49 +2125,49 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.8</v>
+        <v>8.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="12" t="n">
         <v>15.4</v>
       </c>
-      <c r="M20" s="15" t="n">
+      <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2185,10 +2179,10 @@
       <c r="U20" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2214,51 +2208,51 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>261.7</v>
-      </c>
-      <c r="D21" s="11" t="n">
+        <v>251.7</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>7.1</v>
+      <c r="G21" s="12" t="n">
+        <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>11.7</v>
+        <v>1.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99.8</v>
+        <v>90.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R21" s="11" t="n">
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R21" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2270,10 +2264,10 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2299,43 +2293,43 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H22" s="8" t="n">
+      <c r="G22" s="12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="11" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>1.4</v>
+      <c r="L22" s="12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2343,7 +2337,7 @@
       <c r="Q22" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2355,10 +2349,10 @@
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2368,7 +2362,7 @@
         <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2386,33 +2380,33 @@
       <c r="C23" s="3" t="n">
         <v>177.2</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>94.3</v>
+      <c r="E23" s="12" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>61.2</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>12.2</v>
+      <c r="L23" s="12" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>72.2</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>30.4</v>
@@ -2423,14 +2417,14 @@
       <c r="P23" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="14" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="12" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2438,17 +2432,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="11" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="W23" s="10" t="n">
+      <c r="V23" s="14" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>929.5</v>
+        <v>35.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2467,22 +2461,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="12" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>12.9</v>
+        <v>22.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2491,27 +2485,27 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="M24" s="10" t="n">
-        <v>43.4</v>
+      <c r="M24" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>221.1</v>
+        <v>22.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="14" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2523,10 +2517,10 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="11" t="n">
+      <c r="V24" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2552,16 +2546,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>18.8</v>
+      <c r="E25" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9</v>
@@ -2579,10 +2573,10 @@
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>84.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1.5</v>
@@ -2591,14 +2585,14 @@
         <v>91.5</v>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
+      <c r="Q25" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R25" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2606,10 +2600,10 @@
       <c r="U25" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2635,22 +2629,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>326</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="12" t="n">
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2661,14 +2655,14 @@
       <c r="K26" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>1.4</v>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2676,11 +2670,11 @@
       <c r="P26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="R26" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2691,20 +2685,20 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="12" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2720,22 +2714,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" s="12" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
@@ -2744,14 +2738,14 @@
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2759,25 +2753,25 @@
       <c r="P27" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R27" s="3" t="n">
+      <c r="Q27" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>717</v>
+        <v>77</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2803,22 +2797,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>82.8</v>
+        <v>23.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2826,17 +2820,17 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2844,10 +2838,10 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2859,20 +2853,20 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2890,38 +2884,38 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="D29" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" s="12" t="n">
         <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2929,29 +2923,29 @@
       <c r="P29" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q29" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R29" s="3" t="n">
+      <c r="Q29" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R29" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>82.09999999999999</v>
+      <c r="X29" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2975,34 +2969,34 @@
       <c r="C30" s="3" t="n">
         <v>1609.9</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>1129.8</v>
-      </c>
-      <c r="E30" s="14" t="inlineStr"/>
-      <c r="F30" s="10" t="n">
+      <c r="D30" s="14" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="14" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L30" s="14" t="inlineStr"/>
-      <c r="M30" s="10" t="n">
-        <v>11.7</v>
+        <v>9.1</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="12" t="n">
+        <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.9</v>
+        <v>79.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3010,29 +3004,29 @@
       <c r="P30" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="12" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="12" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561</v>
+        <v>361.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="V30" s="10" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="V30" s="14" t="n">
         <v>88.8</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>441</v>
@@ -3056,16 +3050,16 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3079,11 +3073,11 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="10" t="n">
-        <v>14.7</v>
+      <c r="M31" s="12" t="n">
+        <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16.8</v>
@@ -3091,35 +3085,35 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>29.3</v>
+        <v>79.8</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V31" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+      <c r="V31" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>119.2</v>
+        <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>214.4</v>
+        <v>24.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3135,17 +3129,19 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>1.3</v>
+      <c r="G32" s="12" t="n">
+        <v>7.3</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3159,14 +3155,14 @@
       <c r="K32" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M32" s="15" t="n">
+      <c r="L32" s="12" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>10.51</v>
       </c>
-      <c r="N32" s="8" t="n">
-        <v>12.8</v>
+      <c r="N32" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3174,14 +3170,14 @@
       <c r="P32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>18.8</v>
+      <c r="R32" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
@@ -3189,20 +3185,20 @@
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3218,22 +3214,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G33" s="3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>11.7</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>82.59999999999999</v>
+      <c r="H33" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3242,49 +3238,49 @@
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>84.8</v>
+      <c r="N33" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>21.2</v>
+        <v>51.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="12" t="n">
         <v>15.4</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3305,23 +3301,23 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="12" t="n">
         <v>11.5</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>109.5</v>
+      <c r="H34" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.9</v>
@@ -3329,14 +3325,14 @@
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+      <c r="M34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3344,11 +3340,11 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>17.8</v>
+      <c r="R34" s="12" t="n">
+        <v>17.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3359,17 +3355,17 @@
       <c r="U34" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W34" s="3" t="n">
-        <v>12.8</v>
+      <c r="W34" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3386,19 +3382,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>9492.799999999999</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="12" t="n">
         <v>19.3</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>1.1</v>
+      <c r="G35" s="12" t="n">
+        <v>11.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>279.3</v>
@@ -3412,47 +3408,47 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>910</v>
+        <v>10</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="15" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
+      <c r="Q35" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R35" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V35" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V35" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>82.8</v>
+      <c r="W35" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>125.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3471,19 +3467,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9498.9</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E36" s="8" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E36" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="G36" s="15" t="n">
-        <v>41</v>
+      <c r="G36" s="12" t="n">
+        <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
@@ -3497,14 +3493,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="15" t="n">
-        <v>86.59999999999999</v>
+      <c r="L36" s="12" t="n">
+        <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>17.4</v>
+      <c r="N36" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3512,35 +3508,35 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="15" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R36" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V36" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V36" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>66.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3556,15 +3552,15 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2192.8</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="D37" s="14" t="n">
         <v>119.1</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="14" t="n">
         <v>665.7</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="14" t="n">
         <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3572,55 +3568,53 @@
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
-        <v>110.6</v>
+        <v>10.6</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L37" s="10" t="n">
+      <c r="K37" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>75.7</v>
       </c>
-      <c r="M37" s="10" t="n">
-        <v>711.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
+      <c r="M37" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>4420.3</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="12" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>81</v>
+      <c r="R37" s="12" t="n">
+        <v>87</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>313.4</v>
+        <v>13.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="V37" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="12" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.8</v>
+        <v>9.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3639,64 +3633,64 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>438.6</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="14" t="n">
         <v>151.3</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="14" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>82.7</v>
+        <v>62.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="12" t="n">
         <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3722,35 +3716,33 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>39595.3</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G39" s="11" t="n">
+        <v>595.3</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G39" s="12" t="n">
         <v>11.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
+      <c r="M39" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3761,14 +3753,14 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>20.9</v>
+      <c r="S39" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
@@ -3776,11 +3768,11 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="13" t="inlineStr"/>
+      <c r="V39" s="12" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3805,16 +3797,16 @@
       <c r="C40" s="3" t="n">
         <v>545.4</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="D40" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="12" t="n">
         <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -3826,17 +3818,17 @@
       <c r="J40" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>0.8</v>
+      <c r="K40" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>19</v>
+      <c r="M40" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3844,35 +3836,35 @@
       <c r="P40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="3" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>408.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3888,37 +3880,37 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="12" t="n">
         <v>11.2</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>19.2</v>
@@ -3929,35 +3921,35 @@
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="T41" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="X41" s="3" t="n">
-        <v>14.6</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>113.8</v>
+        <v>82</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3973,22 +3965,22 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F42" s="11" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>0.7</v>
+      <c r="G42" s="12" t="n">
+        <v>7.7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
@@ -3996,28 +3988,28 @@
       <c r="J42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>0.9</v>
+      <c r="K42" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>15.1</v>
+        <v>13.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.1</v>
+        <v>19.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4029,20 +4021,20 @@
       <c r="U42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>20.4</v>
+      <c r="V42" s="12" t="n">
+        <v>18.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>18.1</v>
+        <v>22.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>110.1</v>
+        <v>28</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>58</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4058,76 +4050,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>557.1</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>99.59999999999999</v>
+        <v>537</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>35.4</v>
+        <v>16.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V43" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>22.6</v>
+        <v>58</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>557.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4143,76 +4135,74 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2983</v>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>62</v>
+        <v>22.1</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>10.8</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L44" s="15" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R44" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="V44" s="15" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="W44" s="15" t="n">
-        <v>95.5</v>
+      <c r="V44" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>466.8</v>
+        <v>13.6</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>28.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4228,76 +4218,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>497</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G45" s="11" t="n">
-        <v>10.3</v>
+        <v>2983</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.8</v>
+        <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K45" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="14" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="M45" s="10" t="n">
-        <v>0.6</v>
+      <c r="M45" s="14" t="n">
+        <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>10.1</v>
+        <v>540.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>922.8</v>
-      </c>
-      <c r="R45" s="10" t="n">
-        <v>17.1</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q45" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>102.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>97.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>58.5</v>
+        <v>351</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V45" s="10" t="n">
-        <v>118.6</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>15.9</v>
+        <v>69</v>
+      </c>
+      <c r="V45" s="14" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="W45" s="14" t="n">
+        <v>95.90000000000001</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>16.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>82.8</v>
+        <v>468.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>44.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4315,38 +4305,38 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>14.6</v>
+      <c r="D46" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L46" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>12</v>
+      <c r="M46" s="14" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>90.09999999999999</v>
@@ -4354,35 +4344,35 @@
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R46" s="10" t="n">
-        <v>1.8</v>
+      <c r="Q46" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.8</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1414</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="W46" s="10" t="n">
-        <v>11151.1</v>
+        <v>11.5</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="14" t="n">
+        <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.8</v>
+        <v>55.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.1</v>
+        <v>11.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_recheckthresh.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_recheckthresh.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>58.5</v>
+        <v>585.3</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>25</v>
@@ -823,7 +823,7 @@
         <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2.2</v>
@@ -867,16 +867,16 @@
         <v>388.3</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2.7</v>
+        <v>19</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>12.3</v>
@@ -985,7 +985,7 @@
         <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -997,7 +997,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22.9</v>
+        <v>229.6</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>21.6</v>
@@ -1052,25 +1052,25 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29.9</v>
+        <v>27.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1100,7 +1100,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>22.2</v>
+        <v>2224.9</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>118.6</v>
@@ -1149,10 +1149,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1170,7 +1170,7 @@
         <v>86.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>12.6</v>
+        <v>312.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>53</v>
@@ -1222,7 +1222,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>229.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1237,7 +1237,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1255,10 +1255,10 @@
         <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="V9" s="14" t="n">
         <v>94</v>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>45</v>
+        <v>145.5</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>23.7</v>
@@ -1316,7 +1316,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>14.7</v>
@@ -1340,7 +1340,7 @@
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1398,16 +1398,16 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>15.3</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1425,7 +1425,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>212.4</v>
+        <v>22.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1475,17 +1475,17 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="12" t="n">
         <v>14.3</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1556,7 +1556,7 @@
       <c r="K13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M13" s="12" t="n">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
+        <v>324</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>21.8</v>
@@ -1641,7 +1641,7 @@
       <c r="K14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="M14" s="12" t="n">
@@ -1684,7 +1684,7 @@
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
       <c r="K15" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="M15" s="12" t="n">
@@ -1736,7 +1736,7 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1754,7 +1754,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>14.8</v>
+        <v>1475.2</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>114.8</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>674.7</v>
@@ -1809,19 +1809,19 @@
         <v>6.9</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="L16" s="14" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>73.2</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>12.4</v>
+        <v>712.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
@@ -1829,8 +1829,8 @@
       <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="12" t="n">
-        <v>83.5</v>
+      <c r="R16" s="14" t="n">
+        <v>83.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1839,7 +1839,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="V16" s="14" t="n">
         <v>84.3</v>
@@ -1851,7 +1851,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>158.8</v>
+        <v>450.2</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1870,18 +1870,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.5</v>
+        <v>295</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1891,22 +1891,22 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>121.4</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="L17" s="14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>14.6</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.2</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1981,7 +1981,7 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2007,7 +2007,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>18.5</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>40.6</v>
+        <v>440.6</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>25</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2064,7 +2064,7 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2077,7 +2077,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2126,7 +2126,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>13.8</v>
@@ -2135,7 +2135,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.9</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2144,19 +2144,19 @@
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>17.8</v>
+        <v>14.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2177,7 +2177,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>17.6</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>251.7</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>21.9</v>
@@ -2234,14 +2234,14 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2319,14 +2319,14 @@
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>15.5</v>
+      <c r="L22" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.1</v>
+        <v>16.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2393,7 +2393,7 @@
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
@@ -2402,7 +2402,7 @@
       <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="L23" s="14" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="14" t="n">
@@ -2424,7 +2424,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.5</v>
+        <v>90.3</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2433,7 +2433,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="14" t="n">
-        <v>91.3</v>
+        <v>22.8</v>
       </c>
       <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
@@ -2442,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>35.5</v>
+        <v>435.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>29.5</v>
+        <v>295.4</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>22.6</v>
@@ -2476,7 +2476,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2485,19 +2485,19 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L24" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="14" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>22.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2569,7 +2569,7 @@
       <c r="J25" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="12" t="n">
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2579,7 +2579,7 @@
         <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.5</v>
+        <v>15.7</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>91.5</v>
@@ -2652,8 +2652,8 @@
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.9</v>
+      <c r="K26" s="12" t="n">
+        <v>3.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>14.6</v>
@@ -2662,7 +2662,7 @@
         <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2674,7 +2674,7 @@
         <v>20.7</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>288.8</v>
+        <v>287.8</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>23.5</v>
@@ -2735,7 +2735,7 @@
       <c r="J27" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="L27" s="3" t="n">
@@ -2812,7 +2812,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2820,7 +2820,7 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2897,7 +2897,7 @@
         <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13.8</v>
+        <v>33.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.3</v>
@@ -2905,8 +2905,8 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>1.8</v>
+      <c r="K29" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>14.9</v>
@@ -2915,7 +2915,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.1</v>
+        <v>21.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2924,7 +2924,7 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="R29" s="12" t="n">
         <v>17.8</v>
@@ -2988,7 +2988,7 @@
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="K30" s="14" t="n">
+      <c r="K30" s="12" t="n">
         <v>35.6</v>
       </c>
       <c r="L30" s="13" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
         <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3014,13 +3014,13 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.9</v>
+        <v>361.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
       </c>
-      <c r="V30" s="14" t="n">
-        <v>88.8</v>
+      <c r="V30" s="12" t="n">
+        <v>87.8</v>
       </c>
       <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
@@ -3077,10 +3077,10 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
@@ -3092,10 +3092,10 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>18.1</v>
+        <v>181.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.8</v>
+        <v>72.3</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
@@ -3113,7 +3113,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>24.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       <c r="J32" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="L32" s="12" t="n">
@@ -3162,7 +3162,7 @@
         <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3177,13 +3177,13 @@
         <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>15.9</v>
@@ -3198,7 +3198,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3214,22 +3214,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
+        <v>1482.8</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3237,8 +3237,8 @@
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>1.8</v>
+      <c r="K33" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>13.7</v>
@@ -3247,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3314,7 +3314,7 @@
         <v>12.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.3</v>
@@ -3322,7 +3322,7 @@
       <c r="J34" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
@@ -3362,7 +3362,7 @@
         <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>81</v>
@@ -3405,7 +3405,7 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
@@ -3415,10 +3415,10 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>498.9</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>13.9</v>
@@ -3490,7 +3490,7 @@
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
@@ -3500,7 +3500,7 @@
         <v>15.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3533,10 +3533,10 @@
         <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>192.8</v>
+        <v>2192.8</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>119.1</v>
@@ -3573,7 +3573,7 @@
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="L37" s="12" t="n">
@@ -3599,7 +3599,7 @@
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.8</v>
@@ -3611,10 +3611,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>9.5</v>
+        <v>409.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3636,19 +3636,19 @@
         <v>438.6</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.1</v>
@@ -3664,10 +3664,10 @@
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
@@ -3733,16 +3733,18 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>1.5</v>
+        <v>28.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3768,8 +3770,8 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="12" t="inlineStr"/>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="11" t="inlineStr"/>
+      <c r="W39" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3798,7 +3800,7 @@
         <v>545.4</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13.8</v>
@@ -3806,8 +3808,8 @@
       <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>10.7</v>
+      <c r="G40" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3828,7 +3830,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3851,14 +3853,14 @@
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="12" t="n">
+      <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="12" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>82</v>
@@ -3886,7 +3888,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>18.1</v>
@@ -3934,13 +3936,13 @@
         <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V41" s="12" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>18</v>
+      <c r="W41" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3971,7 +3973,7 @@
         <v>22.4</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>18.5</v>
@@ -3995,7 +3997,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.2</v>
+        <v>22.6</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -4021,17 +4023,17 @@
       <c r="U42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4083,7 +4085,7 @@
         <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
@@ -4106,11 +4108,11 @@
       <c r="U43" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V43" s="12" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>15.8</v>
+      <c r="V43" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W43" s="12" t="n">
+        <v>15.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>4.2</v>
@@ -4135,7 +4137,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22.1</v>
+        <v>237.1</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>23.4</v>
@@ -4168,7 +4170,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4181,7 +4183,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4189,10 +4191,10 @@
       <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="V44" s="12" t="n">
+      <c r="V44" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
@@ -4224,7 +4226,7 @@
         <v>141.7</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>97.09999999999999</v>
+        <v>797.1</v>
       </c>
       <c r="F45" s="14" t="n">
         <v>10.5</v>
@@ -4251,7 +4253,7 @@
         <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>540.9</v>
@@ -4260,7 +4262,7 @@
         <v>10.6</v>
       </c>
       <c r="Q45" s="14" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="R45" s="12" t="n">
         <v>102.4</v>
@@ -4278,13 +4280,13 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="14" t="n">
-        <v>95.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>468.8</v>
+        <v>466.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>28.7</v>
@@ -4314,8 +4316,8 @@
       <c r="F46" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>19.3</v>
+      <c r="G46" s="12" t="n">
+        <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>11.8</v>
@@ -4327,13 +4329,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>20.4</v>
+        <v>8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4359,17 +4361,17 @@
       <c r="U46" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="14" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="14" t="n">
+      <c r="W46" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>55.4</v>
+        <v>11.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>11.4</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_recheckthresh.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_recheckthresh.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>585.3</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>25</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.3</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>23.9</v>
@@ -891,13 +891,13 @@
         <v>15.7</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
@@ -982,10 +982,10 @@
         <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -997,7 +997,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17.3</v>
+        <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1052,7 +1052,7 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
@@ -1070,7 +1070,7 @@
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1100,7 +1100,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2224.9</v>
+        <v>222.9</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>118.6</v>
@@ -1149,10 +1149,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>60.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1222,7 +1222,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>229.5</v>
+        <v>22.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1237,7 +1237,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1258,7 +1258,7 @@
         <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="V9" s="14" t="n">
         <v>94</v>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>23.7</v>
@@ -1304,10 +1304,10 @@
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>21.3</v>
@@ -1316,7 +1316,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>14.7</v>
@@ -1398,7 +1398,7 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>15.3</v>
@@ -1407,7 +1407,7 @@
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1425,7 +1425,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22.6</v>
+        <v>2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1452,10 +1452,10 @@
         <v>229.5</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>17.9</v>
@@ -1482,7 +1482,7 @@
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92</v>
@@ -1651,7 +1651,7 @@
         <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
@@ -1703,10 +1703,10 @@
         <v>307.9</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>18.9</v>
@@ -1785,18 +1785,18 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1475.2</v>
+        <v>147.5</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>674.7</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="E16" s="12" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1818,7 +1818,7 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>712.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>14.5</v>
@@ -1829,8 +1829,8 @@
       <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="14" t="n">
-        <v>83.2</v>
+      <c r="R16" s="12" t="n">
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1839,7 +1839,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16" s="14" t="n">
         <v>84.3</v>
@@ -1851,7 +1851,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>450.2</v>
+        <v>450</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1873,13 +1873,13 @@
         <v>295</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>18.6</v>
+        <v>13.6</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>23.3</v>
+        <v>18.3</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>9.5</v>
@@ -1894,7 +1894,7 @@
         <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>14.6</v>
@@ -1903,10 +1903,10 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1981,7 +1981,7 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2007,7 +2007,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>18.5</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2064,7 +2064,7 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="12" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2077,7 +2077,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2126,7 +2126,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>13.8</v>
@@ -2135,7 +2135,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2149,14 +2149,14 @@
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>14.8</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2177,7 +2177,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>17.6</v>
@@ -2234,14 +2234,14 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2319,14 +2319,14 @@
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>22</v>
+      <c r="L22" s="12" t="n">
+        <v>15.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2387,22 +2387,22 @@
         <v>69.40000000000001</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.3</v>
+        <v>64.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" s="12" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="14" t="n">
@@ -2433,7 +2433,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="14" t="n">
-        <v>22.8</v>
+        <v>91.3</v>
       </c>
       <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
@@ -2487,17 +2487,17 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="14" t="n">
+      <c r="L24" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>400.4</v>
+        <v>40</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>22.6</v>
@@ -2745,7 +2745,7 @@
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2812,7 +2812,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>13.8</v>
+        <v>83.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2863,7 +2863,7 @@
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>3.2</v>
@@ -2915,7 +2915,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.2</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2969,8 +2969,8 @@
       <c r="C30" s="3" t="n">
         <v>1609.9</v>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>112.9</v>
+      <c r="D30" s="12" t="n">
+        <v>112.5</v>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="14" t="n">
@@ -3014,7 +3014,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.2</v>
+        <v>36.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
@@ -3077,7 +3077,7 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16</v>
@@ -3092,7 +3092,7 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>181.1</v>
+        <v>181.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>72.3</v>
@@ -3113,7 +3113,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3183,7 +3183,7 @@
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>15.9</v>
@@ -3198,7 +3198,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3214,22 +3214,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>26.6</v>
+        <v>28.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3247,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3332,7 +3332,7 @@
         <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3415,7 +3415,7 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>90</v>
@@ -3430,7 +3430,7 @@
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3470,7 +3470,7 @@
         <v>498.9</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>13.9</v>
@@ -3536,7 +3536,7 @@
         <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.2</v>
+        <v>409</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3645,7 +3645,7 @@
         <v>18.5</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>12.3</v>
@@ -3733,21 +3733,19 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>11.5</v>
+        <v>16</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1.6</v>
+        <v>30.1</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>94</v>
@@ -3808,8 +3806,8 @@
       <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>22.6</v>
+      <c r="G40" s="12" t="n">
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3830,7 +3828,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3860,10 +3858,10 @@
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>6.2</v>
@@ -3888,7 +3886,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>18.1</v>
@@ -3915,7 +3913,7 @@
         <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3942,7 +3940,7 @@
         <v>19</v>
       </c>
       <c r="W41" s="12" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3997,7 +3995,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>22.6</v>
+        <v>13.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -4033,7 +4031,7 @@
         <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4137,7 +4135,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>237.1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>23.4</v>
@@ -4170,7 +4168,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4183,7 +4181,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4220,7 +4218,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2983</v>
+        <v>298</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>141.7</v>
@@ -4280,7 +4278,7 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="14" t="n">
-        <v>22.2</v>
+        <v>95.5</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
@@ -4329,13 +4327,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4368,13 +4366,13 @@
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
